--- a/monitor_xlsx/20260226.xlsx
+++ b/monitor_xlsx/20260226.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2190,112 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7685</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1073</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3006</v>
+      </c>
+      <c r="H21" t="n">
+        <v>28</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-155</v>
+      </c>
+      <c r="J21" t="n">
+        <v>357</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2606</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12250</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-47580</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5719</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-565</v>
+      </c>
+      <c r="G22" t="n">
+        <v>159</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I22" t="n">
+        <v>291</v>
+      </c>
+      <c r="J22" t="n">
+        <v>154</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1931</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9355</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-140163</v>
+      </c>
+      <c r="N22" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260226.xlsx
+++ b/monitor_xlsx/20260226.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2296,165 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>962</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>826</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="G23" t="n">
+        <v>85</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-118</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>624</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>2339</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12425</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>18</v>
+      </c>
+      <c r="K24" t="n">
+        <v>464</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-222</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2642</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-1460</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2855</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-782</v>
+      </c>
+      <c r="I25" t="n">
+        <v>96</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1765</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6387</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-106273</v>
+      </c>
+      <c r="N25" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260226.xlsx
+++ b/monitor_xlsx/20260226.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2455,6 +2455,59 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10139</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1915</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3716</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" t="n">
+        <v>80</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6977</v>
+      </c>
+      <c r="L26" t="n">
+        <v>30975</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-58781</v>
+      </c>
+      <c r="N26" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
